--- a/uploads/mau-nhap-hoat-dong.xlsx
+++ b/uploads/mau-nhap-hoat-dong.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717425BC-9FC3-4944-A341-99C08D32AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66085B92-BC87-4F9F-A5F9-DABB98EE2CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nhap hoat dong" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="119">
   <si>
     <t>STT</t>
   </si>
@@ -207,6 +207,177 @@
   </si>
   <si>
     <t>Tuyên truyền, phổ biến, giáo dục pháp luật, hướng dẫn sử dụng Internet và mạng xã hội an toàn, hiệu quả, đúng pháp luật cho học sinh trường THPT Nguyễn Thị Minh Khai, Quận Bắc Từ Liêm, TP Hà Nội</t>
+  </si>
+  <si>
+    <t>Trường Liên cấp THCS, Tiểu học tư thục Ngôi Sao Hà Nội</t>
+  </si>
+  <si>
+    <t>Các kiến thức, kỹ năm về phòng, chống lừa đảo, "bắt cóc online", xâm hại tình dục và phòng, chống các hành vi vi phạm pháp luật khác trên không gian mạng</t>
+  </si>
+  <si>
+    <t>Trường THCS Phan Chu Trinh, phường Giảng Võ, TP Hà Nội</t>
+  </si>
+  <si>
+    <t>Các kiến thức, kỹ năm về an ninh, an toàn trên không gian mạng, sử dụng Internet an toàn, phòng tránh bắt cóc trực tuyến, phòng tránh lửa đảo trên không gian mạng</t>
+  </si>
+  <si>
+    <t>Trường THCS và THPT Marie Curie</t>
+  </si>
+  <si>
+    <t>Các kiến thức, kỹ năm bảo đảm an ninh, an toàn khi sử dụng mạng Internet, mạng xã hội, các kiến thức phòng, chống lừa đảo, "bắt cóc online", xâm hại tình dục và phòng, chống các hành vi vi phạm pháp luật khác trên không gian mạng</t>
+  </si>
+  <si>
+    <t>An ninh, an toàn trên không gian mạng cho học sinh nhà trường</t>
+  </si>
+  <si>
+    <t>Trường THCS và THPT Marie Curie Long Biên</t>
+  </si>
+  <si>
+    <t>Kỹ năng đảm bảo an ninh, an toàn trên không gian mạng</t>
+  </si>
+  <si>
+    <t>Trường THCS Giảng Võ, phường Giảng Võ, TP Hà Nội</t>
+  </si>
+  <si>
+    <t>Các kiến thức, kỹ năng về an ninh, an toàn trên không gian mạng, sử dụng internet an toàn, phòng tránh bắt cóc trực tuyến, phòng tránh lừa đảo trên không gian mạng cho học sinh</t>
+  </si>
+  <si>
+    <t>Trường THCS Nguyễn Trãi, phường Giảng Võ, TP Hà Nội</t>
+  </si>
+  <si>
+    <t>Chuyên đề pháp luật vè an ninh mạng, sử dụng Internet an toàn cho học sinh của nhà trường</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trường Tiểu học Đoàn Thị Điểm </t>
+  </si>
+  <si>
+    <t>Các kiến thức, kỹ năng cần thiết để tự bảo vệ bản thân khi tham gia môi trường mạng (nhận biết thông tin xấu độc, bảo mật tài khoản, phòng tránh lừa đảo trực tuyến, phòng tránh nguy cơ bị bắt cóc, xâm hại, sử dụng dịch vụ xe công nghệ an toàn,…)</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Đoàn Thị Điểm (Symphony) - Hà Nội</t>
+  </si>
+  <si>
+    <t>Em an toàn mọi lúc, mọi nơi</t>
+  </si>
+  <si>
+    <t>Trường Phổ thông Dân tộc bán trú Tiểu học Vừ A Dính, thôn Có Thái, xã Nậm Có, tỉnh Lào Cai</t>
+  </si>
+  <si>
+    <t>An toàn thông tin - Kỹ năng cần thiết cho học sinh tiểu học</t>
+  </si>
+  <si>
+    <t>Uỷ ban Mặt trận Tổ quốc Việt Nam phường Xuân Đỉnh, TP Hà Nội</t>
+  </si>
+  <si>
+    <t>Tuyên truyền pháp luật về an ninh mạng; phổ biến, hướng dẫn sử dụng Internet, mạng xã hội an toàn, văn minh, đúng pháp luật và cách bảo mật thông tin các nhân trên Internet</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Trung Tự, phường Kim Liên, TP Hà Nội</t>
+  </si>
+  <si>
+    <t>Em an toàn trên môi trường mạng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hvcsnd.edu.vn/tuyen-truyen-trang-bi-ky-nang-su-dung-mang-xa-hoi-an-toan-cho-hoc-sinh-truong-thcs-xuan-truong-nam-dinh-12636 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hvcsnd.edu.vn/tuyen-truyen-huong-dan-su-dung-internet-va-giao-tiep-ung-xu-tren-khong-gian-mang-11869 </t>
+  </si>
+  <si>
+    <t>https://hvcsnd.edu.vn/khoa-toan-tin-hoc-va-ung-dung-khcn-trong-pctp-tuyen-truyen-pho-bien-giao-duc-phap-luat-cho-hoc-sinh-tai-ha-noi-11252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hvcsnd.edu.vn/khoa-toan-tin-hoc-va-ung-dung-khcn-trong-pctp-tuyen-truyen-pho-bien-giao-duc-phap-luat-cho-hoc-sinh-tai-ha-noi-11252 </t>
+  </si>
+  <si>
+    <t>Trường THCS Phúc Diễn</t>
+  </si>
+  <si>
+    <t>Thiện nguyện</t>
+  </si>
+  <si>
+    <t>Tuyên truyền sử dụng mạng xã hội an toàn, có hiệu quả vì một môi trường mạng xã hội bình yên</t>
+  </si>
+  <si>
+    <t>15,16/11/2024</t>
+  </si>
+  <si>
+    <t>2 điểm trường Pa Cốp và Gốc Đa của trường Tiểu học Vân Hồ, xã Vân Hồ, huyện Vân Hồ, tỉnh Sơn La</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học và THCS Vần Dính, xã Thượng Thôn, huyện Quảng Hà, tỉnh Cao Bằng</t>
+  </si>
+  <si>
+    <t>02,03/02/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ngoisaohanoi.edu.vn/ngoi-sao-ha-noi-chu-dong-trang-bi-la-chan-an-toan-cho-hansers-khoi-trung-hoc-co-so/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://c2giangvo2.giangvo.edu.vn/chi-tiet/truong-thcs-giang-vo-2-to-chuc-tuyen-truyen-an-toa-pmtd22sw25208 </t>
+  </si>
+  <si>
+    <t>An toàn, an ninh mạng</t>
+  </si>
+  <si>
+    <t>Trường THCS Giảng Võ 2, TP Hà Nội</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hvcsnd.edu.vn/hanh-trinh-se-chia-yeu-thuong-tai-truong-pho-thong-dan-toc-ban-tru-tieu-hoc-vu-a-dinh-xa-nam-co-tinh-lao-cai-13680 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hn-ams.edu.vn/en/node/39102 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hvcsnd.edu.vn/tuyen-truyen-pho-bien-giao-duc-phap-luat-huong-dan-su-dung-internet-va-mang-xa-hoi-an-toan-hieu-qua-11155 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://anninhthudo.vn/tuyen-truyen-su-dung-internet-mang-xa-hoi-an-toan-cho-hoc-sinh-post627307.antd </t>
+  </si>
+  <si>
+    <t>Có 3 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Vần dính</t>
+  </si>
+  <si>
+    <t>Có 2 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Pacop</t>
+  </si>
+  <si>
+    <t>Có 3 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Vừ a dính</t>
+  </si>
+  <si>
+    <t>Có 11 ảnh ở thư mục C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Nguyễn Thị Minh Khai</t>
+  </si>
+  <si>
+    <t>Có 6 ảnh ở thư mục C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Hà Nội Arm</t>
+  </si>
+  <si>
+    <t>Có 6 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Cầu giấy 2</t>
+  </si>
+  <si>
+    <t>Có 2 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Thượng cát</t>
+  </si>
+  <si>
+    <t>Có 6 ảnh ở thư mục C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Cầu giấy</t>
+  </si>
+  <si>
+    <t>Có 4 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Xuân Đỉnh</t>
+  </si>
+  <si>
+    <t>Có 4 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Ngôi sao Hà Nội</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/p/1SE5BUFGcc/</t>
+  </si>
+  <si>
+    <t>Có 10 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Marie Curie</t>
+  </si>
+  <si>
+    <t>Có 8 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Đoàn Thị Điểm</t>
+  </si>
+  <si>
+    <t>https://hvcsnd.edu.vn/hoc-vien-csnd-phoi-hop-truong-thcs-tran-duy-hung-to-chuc-chuong-trinh-em-an-toan-tren-moi-truong-mang-13270</t>
+  </si>
+  <si>
+    <t>Có 3 ảnh ở C:\Users\VUONGNQ\Desktop\TUYEN_TRUYEN\uploads\Mai Dịch</t>
   </si>
 </sst>
 </file>
@@ -308,7 +479,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -370,25 +541,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -434,17 +592,20 @@
     <xf numFmtId="14" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" style="6" customWidth="1"/>
@@ -758,7 +919,7 @@
     <col min="3" max="3" width="18" style="6" customWidth="1"/>
     <col min="4" max="4" width="27.77734375" style="6" customWidth="1"/>
     <col min="5" max="5" width="16" style="6" customWidth="1"/>
-    <col min="6" max="6" width="34.44140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="52" style="6" customWidth="1"/>
     <col min="7" max="7" width="46" style="6" customWidth="1"/>
     <col min="8" max="10" width="30" style="6" customWidth="1"/>
     <col min="11" max="16384" width="8.77734375" style="6"/>
@@ -826,242 +987,294 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="82.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="9"/>
+      <c r="B3" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="C3" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="E3" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>94</v>
+      </c>
       <c r="G3" s="9"/>
       <c r="H3" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J3" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="76.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="C4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
+      <c r="E4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="22" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J4" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="102" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="E5" s="12">
+        <v>46017</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="G5" s="9"/>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="22" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J5" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9" t="s">
-        <v>60</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="9"/>
       <c r="E6" s="12">
-        <v>44788</v>
+        <v>44285</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="H6" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="16">
-        <v>44839</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>51</v>
+      <c r="D7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="12">
+        <v>44788</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="H7" s="20" t="s">
+        <v>102</v>
+      </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="J7" s="9" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="19">
-        <v>44841</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="C8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="16">
+        <v>44839</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="17">
+        <v>44841</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E10" s="17">
         <v>44875</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F10" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="19">
-        <v>44881</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>56</v>
-      </c>
       <c r="G10" s="14"/>
-      <c r="H10" s="11"/>
+      <c r="H10" s="21" t="s">
+        <v>88</v>
+      </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="J10" s="9" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="19">
-        <v>45167</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>34</v>
+        <v>57</v>
+      </c>
+      <c r="E11" s="17">
+        <v>44881</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="G11" s="14"/>
-      <c r="H11" s="9"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="19">
-        <v>45189</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>46</v>
+        <v>33</v>
+      </c>
+      <c r="E12" s="17">
+        <v>45167</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="G12" s="14"/>
-      <c r="H12" s="9"/>
+      <c r="H12" s="20" t="s">
+        <v>86</v>
+      </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="J12" s="9" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="21">
-        <v>45208</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
+      </c>
+      <c r="E13" s="17">
+        <v>45189</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="9"/>
@@ -1070,159 +1283,249 @@
     </row>
     <row r="14" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="21">
-        <v>45432</v>
+        <v>36</v>
+      </c>
+      <c r="E14" s="19">
+        <v>45208</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G14" s="14"/>
-      <c r="H14" s="9"/>
+      <c r="H14" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="J14" s="9" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="21">
-        <v>45597</v>
+        <v>38</v>
+      </c>
+      <c r="E15" s="19">
+        <v>45432</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G15" s="14"/>
-      <c r="H15" s="9"/>
+      <c r="H15" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="19">
+        <v>45597</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="20" t="s">
+        <v>85</v>
+      </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="52.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
-        <v>9</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="E17" s="12">
+        <v>45940</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="H17" s="20" t="s">
+        <v>96</v>
+      </c>
       <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J17" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="55.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
-        <v>10</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="E18" s="12">
+        <v>45946</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="H18" s="20" t="s">
+        <v>103</v>
+      </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
-        <v>11</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="E19" s="12">
+        <v>45955</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="H19" s="20" t="s">
+        <v>114</v>
+      </c>
       <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
-        <v>12</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="E20" s="12">
+        <v>45965</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
-        <v>13</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="E21" s="12">
+        <v>45966</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="J21" s="9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
-        <v>14</v>
-      </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="E22" s="12">
+        <v>46017</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="J22" s="9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
-        <v>15</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+      <c r="E23" s="12">
+        <v>45957</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -1230,13 +1533,21 @@
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
-        <v>16</v>
-      </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
+      <c r="E24" s="12">
+        <v>45968</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -1244,13 +1555,21 @@
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
-        <v>17</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
+      <c r="E25" s="12">
+        <v>45968</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -1258,77 +1577,125 @@
     </row>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
-        <v>18</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
+      <c r="E26" s="12">
+        <v>45978</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="J26" s="9" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
-        <v>19</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
+      <c r="E27" s="12">
+        <v>45985</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J27" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
-        <v>20</v>
-      </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="E28" s="12">
+        <v>46017</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="H28" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
-        <v>21</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
+      <c r="E29" s="12">
+        <v>46038</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="46.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
-        <v>22</v>
-      </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="E30" s="12">
+        <v>46112</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
+      <c r="H30" s="20" t="s">
+        <v>97</v>
+      </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1342,7 +1709,7 @@
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1354,93 +1721,9 @@
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
-        <v>25</v>
-      </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
-        <v>26</v>
-      </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
-        <v>27</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8">
-        <v>28</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8">
-        <v>29</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8">
-        <v>30</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Phân loại không hợp lệ" error="Chọn 1 trong 5 phân loại có sẵn" sqref="D16:D39 C3:C39 D3:D7" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Phân loại không hợp lệ" error="Chọn 1 trong 5 phân loại có sẵn" sqref="D3:D8 C3:C16 C17:D33" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"An ninh mạng,Chuyển đổi số,Đổi mới sáng tạo,Nghiên cứu khoa học,Khác"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1448,6 +1731,17 @@
     <hyperlink ref="H3" r:id="rId1" xr:uid="{4828F916-DF36-6C4C-8558-FEA4D5FDB669}"/>
     <hyperlink ref="H4" r:id="rId2" xr:uid="{A7ECF054-C530-1845-B60B-097AE7F9D483}"/>
     <hyperlink ref="H5" r:id="rId3" xr:uid="{18E5B789-1E63-F642-9F4E-2D9E488140BD}"/>
+    <hyperlink ref="H16" r:id="rId4" xr:uid="{950D7AD0-3875-D742-BF32-206FFC45FC1E}"/>
+    <hyperlink ref="H12" r:id="rId5" xr:uid="{1D6236FD-EDE9-204D-B735-ED9C2100729A}"/>
+    <hyperlink ref="H10" r:id="rId6" xr:uid="{991E11A3-E531-3645-A17E-042F2D685967}"/>
+    <hyperlink ref="H9" r:id="rId7" xr:uid="{8C33CB3E-24FD-9743-B209-772ECD1B64B5}"/>
+    <hyperlink ref="H17" r:id="rId8" xr:uid="{166B5CE2-015D-884F-9BA0-97D88EEAFDFD}"/>
+    <hyperlink ref="H30" r:id="rId9" xr:uid="{1C8C8623-EE3F-B84D-A2C6-90F5890BC3E5}"/>
+    <hyperlink ref="H28" r:id="rId10" xr:uid="{C30DAB19-68BF-5140-AB20-7B55C7948F3A}"/>
+    <hyperlink ref="I8" r:id="rId11" xr:uid="{81789C96-391F-CB48-A5C8-52BFFE1FD79D}"/>
+    <hyperlink ref="H7" r:id="rId12" xr:uid="{6E63F5B3-8B2F-BA4E-A444-4E65AC4E78A0}"/>
+    <hyperlink ref="H18" r:id="rId13" xr:uid="{B596814D-D0DE-C041-9382-C89837C824BD}"/>
+    <hyperlink ref="H19" r:id="rId14" xr:uid="{99F4BCF6-49AF-4CA5-B401-56A9FF0365FC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
